--- a/light_fight/Assets/Excels/MonsterConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterConfig.xlsx
@@ -74,9 +74,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -149,7 +148,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -345,107 +344,107 @@
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="17.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="6.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="8.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="6.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="6.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="17.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="6.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="8.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="6.85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1" t="b">
+      <c r="D2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="0" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F2" s="0" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="I2" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K2" s="1" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="J2" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="0" t="n">
+      <c r="M2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="N2" s="0" t="n">
+      <c r="N2" s="1" t="n">
         <v>20</v>
       </c>
     </row>

--- a/light_fight/Assets/Excels/MonsterConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterConfig.xlsx
@@ -418,7 +418,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>100000</v>

--- a/light_fight/Assets/Excels/MonsterConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t xml:space="preserve">monsterId</t>
   </si>
@@ -34,9 +34,6 @@
     <t xml:space="preserve">isRanged</t>
   </si>
   <si>
-    <t xml:space="preserve">radius</t>
-  </si>
-  <si>
     <t xml:space="preserve">skillId</t>
   </si>
   <si>
@@ -67,7 +64,7 @@
     <t xml:space="preserve">Smile</t>
   </si>
   <si>
-    <t xml:space="preserve">Monster_10000</t>
+    <t xml:space="preserve">Unit Goose</t>
   </si>
 </sst>
 </file>
@@ -341,23 +338,22 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="6.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="17.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="6.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="8.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="6.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="6.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="8.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="6.85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -400,51 +396,45 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>10000</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>0.5</v>
+        <v>100000</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>1.25</v>
-      </c>
       <c r="L2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="1" t="n">
         <v>20</v>
       </c>
     </row>

--- a/light_fight/Assets/Excels/MonsterConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterConfig.xlsx
@@ -417,7 +417,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>3</v>

--- a/light_fight/Assets/Excels/MonsterConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t xml:space="preserve">monsterId</t>
   </si>
@@ -53,9 +53,6 @@
   </si>
   <si>
     <t xml:space="preserve">attack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">defense</t>
   </si>
   <si>
     <t xml:space="preserve">health</t>
@@ -338,7 +335,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.33"/>
@@ -352,8 +349,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="6.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="8.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="6.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="6.85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -393,19 +389,16 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>10000</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>0</v>
@@ -417,7 +410,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>3</v>
@@ -432,9 +425,6 @@
         <v>1</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="1" t="n">
         <v>20</v>
       </c>
     </row>

--- a/light_fight/Assets/Excels/MonsterConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t xml:space="preserve">monsterId</t>
   </si>
@@ -58,10 +58,16 @@
     <t xml:space="preserve">health</t>
   </si>
   <si>
-    <t xml:space="preserve">Smile</t>
+    <t xml:space="preserve">Goose</t>
   </si>
   <si>
     <t xml:space="preserve">Unit Goose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cowboy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit Cowboy</t>
   </si>
 </sst>
 </file>
@@ -335,7 +341,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.33"/>
@@ -419,13 +425,51 @@
         <v>0.2</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="K2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L2" s="1" t="n">
         <v>20</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>10010</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>100010</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/light_fight/Assets/Excels/MonsterConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterConfig.xlsx
@@ -460,10 +460,10 @@
         <v>2.25</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>2</v>

--- a/light_fight/Assets/Excels/MonsterConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t xml:space="preserve">monsterId</t>
   </si>
@@ -28,9 +28,6 @@
     <t xml:space="preserve">monsterName</t>
   </si>
   <si>
-    <t xml:space="preserve">monsterObjectId</t>
-  </si>
-  <si>
     <t xml:space="preserve">isRanged</t>
   </si>
   <si>
@@ -61,13 +58,7 @@
     <t xml:space="preserve">Goose</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit Goose</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cowboy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit Cowboy</t>
   </si>
 </sst>
 </file>
@@ -341,21 +332,20 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="6.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="6.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="17.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="13.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="6.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="6.85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -392,45 +382,39 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>10000</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>3</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="1" t="n">
         <v>20</v>
       </c>
     </row>
@@ -439,36 +423,33 @@
         <v>10010</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
+        <v>100010</v>
+      </c>
+      <c r="E3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>100010</v>
-      </c>
       <c r="F3" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H3" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="H3" s="1" t="n">
-        <v>2.25</v>
-      </c>
       <c r="I3" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" s="1" t="n">
         <v>18</v>
       </c>
     </row>

--- a/light_fight/Assets/Excels/MonsterConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterConfig.xlsx
@@ -385,7 +385,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
-        <v>10000</v>
+        <v>10001</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>11</v>
@@ -394,7 +394,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>100000</v>
+        <v>110010</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>1</v>
@@ -420,7 +420,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>10010</v>
+        <v>10002</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
@@ -429,7 +429,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>100010</v>
+        <v>110020</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>1</v>

--- a/light_fight/Assets/Excels/MonsterConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterConfig.xlsx
@@ -420,7 +420,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>10002</v>
+        <v>10011</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>

--- a/light_fight/Assets/Excels/MonsterConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterConfig.xlsx
@@ -385,7 +385,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
-        <v>10001</v>
+        <v>1001</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>11</v>
@@ -394,7 +394,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>110010</v>
+        <v>1001</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>1</v>
@@ -420,7 +420,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>10011</v>
+        <v>1002</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
@@ -429,7 +429,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>110020</v>
+        <v>1002</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>1</v>

--- a/light_fight/Assets/Excels/MonsterConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t xml:space="preserve">skillCooldown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">radius</t>
   </si>
   <si>
     <t xml:space="preserve">moveSpeed</t>
@@ -137,12 +140,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -335,7 +342,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.02"/>
@@ -344,11 +351,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="6.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="6.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="11.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="17.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="6.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="6.85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -388,19 +395,22 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>1001</v>
+        <v>10001</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>1</v>
@@ -409,33 +419,36 @@
         <v>3</v>
       </c>
       <c r="H2" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I2" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I2" s="1" t="n">
+      <c r="J2" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="K2" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="L2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="1" t="n">
+      <c r="M2" s="1" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>1002</v>
+      <c r="A3" s="2" t="n">
+        <v>1011</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>1002</v>
+      <c r="E3" s="2" t="n">
+        <v>10011</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>1</v>
@@ -444,18 +457,21 @@
         <v>3</v>
       </c>
       <c r="H3" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I3" s="1" t="n">
         <v>2.25</v>
       </c>
-      <c r="I3" s="1" t="n">
+      <c r="J3" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="K3" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="L3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L3" s="1" t="n">
+      <c r="M3" s="1" t="n">
         <v>18</v>
       </c>
     </row>

--- a/light_fight/Assets/Excels/MonsterConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -64,7 +64,13 @@
     <t xml:space="preserve">Goose</t>
   </si>
   <si>
+    <t xml:space="preserve">1001 Monster</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cowboy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1002 Monster</t>
   </si>
 </sst>
 </file>
@@ -347,7 +353,8 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="9.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.26"/>
@@ -406,11 +413,14 @@
       <c r="B2" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="D2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>10001</v>
+        <v>10010</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>1</v>
@@ -439,16 +449,19 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="n">
-        <v>1011</v>
+        <v>1002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10011</v>
+        <v>10020</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>1</v>

--- a/light_fight/Assets/Excels/MonsterConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterConfig.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Idle-rpg\light_fight\Assets\Excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48E85CB-3C86-4245-9B5D-38AC6A9D52BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="1020" yWindow="4752" windowWidth="17280" windowHeight="6624" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="monsters" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="monsters" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -22,86 +27,68 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">isRanged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skillId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skillLevel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skillCooldown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">radius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">moveSpeed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stopMoveDistance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attackDistance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1001 Monster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cowboy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1002 Monster</t>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>isRanged</t>
+  </si>
+  <si>
+    <t>skillId</t>
+  </si>
+  <si>
+    <t>skillLevel</t>
+  </si>
+  <si>
+    <t>skillCooldown</t>
+  </si>
+  <si>
+    <t>radius</t>
+  </si>
+  <si>
+    <t>moveSpeed</t>
+  </si>
+  <si>
+    <t>stopMoveDistance</t>
+  </si>
+  <si>
+    <t>attackDistance</t>
+  </si>
+  <si>
+    <t>attack</t>
+  </si>
+  <si>
+    <t>health</t>
+  </si>
+  <si>
+    <t>Goose</t>
+  </si>
+  <si>
+    <t>Cowboy</t>
+  </si>
+  <si>
+    <t>2002 Monster</t>
+  </si>
+  <si>
+    <t>2001 Monster</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -113,7 +100,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -121,105 +108,77 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -251,7 +210,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -275,7 +234,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -335,164 +294,162 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="11.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="17.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="6.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="6.85"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="8.5546875" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" customWidth="1"/>
+    <col min="5" max="5" width="8.21875" customWidth="1"/>
+    <col min="6" max="6" width="8.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="8" max="9" width="11.44140625" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" customWidth="1"/>
+    <col min="11" max="11" width="13.77734375" customWidth="1"/>
+    <col min="12" max="12" width="6.6640625" customWidth="1"/>
+    <col min="13" max="13" width="6.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>1001</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2001</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>3001</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>0.4</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>0.2</v>
+      </c>
+      <c r="K2">
+        <v>1.2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2002</v>
+      </c>
+      <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>10010</v>
-      </c>
-      <c r="F2" s="1" t="n">
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="E3">
+        <v>3002</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
         <v>3</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="H3">
         <v>0.4</v>
       </c>
-      <c r="I2" s="1" t="n">
+      <c r="I3">
+        <v>2.25</v>
+      </c>
+      <c r="J3">
         <v>3</v>
       </c>
-      <c r="J2" s="1" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="1" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
-        <v>1002</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>10020</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" s="1" t="n">
+      <c r="K3">
         <v>4</v>
       </c>
-      <c r="L3" s="1" t="n">
+      <c r="L3">
         <v>2</v>
       </c>
-      <c r="M3" s="1" t="n">
+      <c r="M3">
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>

--- a/light_fight/Assets/Excels/MonsterConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Idle-rpg\light_fight\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48E85CB-3C86-4245-9B5D-38AC6A9D52BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA22B95-D401-446D-9850-1F6CECA61054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="4752" windowWidth="17280" windowHeight="6624" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="14400" windowHeight="8300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monsters" sheetId="1" r:id="rId1"/>
@@ -307,23 +307,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="8.5546875" customWidth="1"/>
+    <col min="2" max="2" width="8.54296875" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" customWidth="1"/>
-    <col min="5" max="5" width="8.21875" customWidth="1"/>
-    <col min="6" max="6" width="8.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
-    <col min="8" max="9" width="11.44140625" customWidth="1"/>
-    <col min="10" max="10" width="17.33203125" customWidth="1"/>
-    <col min="11" max="11" width="13.77734375" customWidth="1"/>
-    <col min="12" max="12" width="6.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.88671875" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" customWidth="1"/>
+    <col min="5" max="5" width="8.1796875" customWidth="1"/>
+    <col min="6" max="6" width="8.81640625" customWidth="1"/>
+    <col min="7" max="7" width="13.1796875" customWidth="1"/>
+    <col min="8" max="9" width="11.453125" customWidth="1"/>
+    <col min="10" max="10" width="17.36328125" customWidth="1"/>
+    <col min="11" max="11" width="13.81640625" customWidth="1"/>
+    <col min="12" max="12" width="6.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -364,7 +364,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2001</v>
       </c>
@@ -393,7 +393,7 @@
         <v>3</v>
       </c>
       <c r="J2">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>1.2</v>
@@ -405,7 +405,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2002</v>
       </c>
@@ -434,7 +434,7 @@
         <v>2.25</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K3">
         <v>4</v>

--- a/light_fight/Assets/Excels/MonsterConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Idle-rpg\light_fight\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA22B95-D401-446D-9850-1F6CECA61054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC07570-3096-4CAC-A077-531706030F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="14400" windowHeight="8300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monsters" sheetId="1" r:id="rId1"/>
@@ -25,13 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>path</t>
   </si>
@@ -45,9 +39,6 @@
     <t>skillLevel</t>
   </si>
   <si>
-    <t>skillCooldown</t>
-  </si>
-  <si>
     <t>radius</t>
   </si>
   <si>
@@ -76,6 +67,42 @@
   </si>
   <si>
     <t>2001 Monster</t>
+  </si>
+  <si>
+    <t>monsterId</t>
+  </si>
+  <si>
+    <t>monsterName</t>
+  </si>
+  <si>
+    <t>BASE</t>
+  </si>
+  <si>
+    <t>SKILL</t>
+  </si>
+  <si>
+    <t>CONFIG</t>
+  </si>
+  <si>
+    <t>defense</t>
+  </si>
+  <si>
+    <t>attackSpeed</t>
+  </si>
+  <si>
+    <t>criticalRate</t>
+  </si>
+  <si>
+    <t>criticalDamage</t>
+  </si>
+  <si>
+    <t>damageMultiplier</t>
+  </si>
+  <si>
+    <t>armorPenPercent</t>
+  </si>
+  <si>
+    <t>STAT</t>
   </si>
 </sst>
 </file>
@@ -91,17 +118,59 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -111,8 +180,44 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -306,149 +411,190 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="8.54296875" customWidth="1"/>
+    <col min="1" max="1" width="10.08984375" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="9.08984375" customWidth="1"/>
-    <col min="5" max="5" width="8.1796875" customWidth="1"/>
-    <col min="6" max="6" width="8.81640625" customWidth="1"/>
-    <col min="7" max="7" width="13.1796875" customWidth="1"/>
-    <col min="8" max="9" width="11.453125" customWidth="1"/>
-    <col min="10" max="10" width="17.36328125" customWidth="1"/>
-    <col min="11" max="11" width="13.81640625" customWidth="1"/>
-    <col min="12" max="12" width="6.6328125" customWidth="1"/>
-    <col min="13" max="13" width="6.90625" customWidth="1"/>
+    <col min="4" max="4" width="10.6328125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="10.6328125" style="8" customWidth="1"/>
+    <col min="6" max="6" width="10.6328125" style="9" customWidth="1"/>
+    <col min="7" max="7" width="15.6328125" style="12" customWidth="1"/>
+    <col min="8" max="9" width="15.6328125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="15.6328125" style="9" customWidth="1"/>
+    <col min="11" max="18" width="15.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="14"/>
+      <c r="G1" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+    </row>
+    <row r="2" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2001</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="12">
+        <v>0</v>
+      </c>
+      <c r="E3" s="8">
+        <v>3001</v>
+      </c>
+      <c r="F3" s="9">
+        <v>1</v>
+      </c>
+      <c r="G3" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="H3" s="8">
+        <v>3</v>
+      </c>
+      <c r="I3" s="8">
+        <v>3</v>
+      </c>
+      <c r="J3" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2002</v>
+      </c>
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="C4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>2001</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>3001</v>
-      </c>
-      <c r="F2">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
+      <c r="E4" s="8">
+        <v>3002</v>
+      </c>
+      <c r="F4" s="9">
+        <v>1</v>
+      </c>
+      <c r="G4" s="12">
         <v>0.4</v>
       </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>1.2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>2002</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>3002</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>0.4</v>
-      </c>
-      <c r="I3">
+      <c r="H4" s="8">
         <v>2.25</v>
       </c>
-      <c r="J3">
+      <c r="I4" s="8">
         <v>6</v>
       </c>
-      <c r="K3">
+      <c r="J4" s="9">
         <v>4</v>
       </c>
-      <c r="L3">
+      <c r="K4">
         <v>2</v>
       </c>
-      <c r="M3">
+      <c r="L4">
         <v>18</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:R1"/>
+  </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>

--- a/light_fight/Assets/Excels/MonsterConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Idle-rpg\light_fight\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC07570-3096-4CAC-A077-531706030F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{872A7DE3-B186-4BF9-9F30-AEE58B11364D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,14 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>path</t>
   </si>
   <si>
-    <t>isRanged</t>
-  </si>
-  <si>
     <t>skillId</t>
   </si>
   <si>
@@ -48,21 +45,12 @@
     <t>stopMoveDistance</t>
   </si>
   <si>
-    <t>attackDistance</t>
-  </si>
-  <si>
     <t>attack</t>
   </si>
   <si>
     <t>health</t>
   </si>
   <si>
-    <t>Goose</t>
-  </si>
-  <si>
-    <t>Cowboy</t>
-  </si>
-  <si>
     <t>2002 Monster</t>
   </si>
   <si>
@@ -75,15 +63,6 @@
     <t>monsterName</t>
   </si>
   <si>
-    <t>BASE</t>
-  </si>
-  <si>
-    <t>SKILL</t>
-  </si>
-  <si>
-    <t>CONFIG</t>
-  </si>
-  <si>
     <t>defense</t>
   </si>
   <si>
@@ -102,7 +81,58 @@
     <t>armorPenPercent</t>
   </si>
   <si>
-    <t>STAT</t>
+    <t>Monster_1</t>
+  </si>
+  <si>
+    <t>Monster_2</t>
+  </si>
+  <si>
+    <t>Monster_3</t>
+  </si>
+  <si>
+    <t>2003 Monster</t>
+  </si>
+  <si>
+    <t>Monster_4</t>
+  </si>
+  <si>
+    <t>2004 Monster</t>
+  </si>
+  <si>
+    <t>Monster_5</t>
+  </si>
+  <si>
+    <t>2005 Monster</t>
+  </si>
+  <si>
+    <t>Monster_6</t>
+  </si>
+  <si>
+    <t>2006 Monster</t>
+  </si>
+  <si>
+    <t>Monster_7</t>
+  </si>
+  <si>
+    <t>2007 Monster</t>
+  </si>
+  <si>
+    <t>Monster_8</t>
+  </si>
+  <si>
+    <t>2008 Monster</t>
+  </si>
+  <si>
+    <t>Monster_9</t>
+  </si>
+  <si>
+    <t>2009 Monster</t>
+  </si>
+  <si>
+    <t>Monster_10</t>
+  </si>
+  <si>
+    <t>2010 Monster</t>
   </si>
 </sst>
 </file>
@@ -118,36 +148,12 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -180,43 +186,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -411,188 +398,571 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="10.6328125" style="12" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" style="8" customWidth="1"/>
-    <col min="6" max="6" width="10.6328125" style="9" customWidth="1"/>
-    <col min="7" max="7" width="15.6328125" style="12" customWidth="1"/>
-    <col min="8" max="9" width="15.6328125" style="8" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" style="9" customWidth="1"/>
-    <col min="11" max="18" width="15.6328125" customWidth="1"/>
+    <col min="1" max="1" width="10.08984375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="6" customWidth="1"/>
+    <col min="3" max="3" width="20" style="6" customWidth="1"/>
+    <col min="4" max="4" width="10.6328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6328125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.6328125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="15.6328125" customWidth="1"/>
+    <col min="8" max="8" width="15.6328125" style="3" customWidth="1"/>
+    <col min="9" max="16" width="15.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="13" t="s">
+      <c r="P1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="14"/>
-      <c r="G1" s="10" t="s">
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>2001</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="3" t="s">
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1">
+        <v>3001</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="G2" s="1">
+        <v>2</v>
+      </c>
+      <c r="H2" s="2">
+        <v>3</v>
+      </c>
+      <c r="I2" s="1">
+        <v>5</v>
+      </c>
+      <c r="J2" s="1">
+        <v>20</v>
+      </c>
+      <c r="K2" s="1">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1">
+        <v>1</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="O2" s="1">
+        <v>1</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>2002</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1">
+        <v>3002</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H3" s="2">
+        <v>3</v>
+      </c>
+      <c r="I3" s="1">
+        <v>7</v>
+      </c>
+      <c r="J3" s="1">
+        <v>30</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1.05</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="N3" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="O3" s="1">
+        <v>1.05</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>2003</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3003</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="H4" s="2">
+        <v>3</v>
+      </c>
+      <c r="I4" s="1">
+        <v>9</v>
+      </c>
+      <c r="J4" s="1">
+        <v>40</v>
+      </c>
+      <c r="K4" s="1">
+        <v>2</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="N4" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="O4" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>2004</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="1">
+        <v>3004</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="H5" s="2">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1">
+        <v>11</v>
+      </c>
+      <c r="J5" s="1">
+        <v>50</v>
+      </c>
+      <c r="K5" s="1">
+        <v>3</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="N5" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="O5" s="1">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>2005</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-    </row>
-    <row r="2" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="D6" s="1">
+        <v>3005</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="G6" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="H6" s="2">
+        <v>3</v>
+      </c>
+      <c r="I6" s="1">
+        <v>13</v>
+      </c>
+      <c r="J6" s="1">
+        <v>60</v>
+      </c>
+      <c r="K6" s="1">
+        <v>4</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="N6" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="O6" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>2006</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3006</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="G7" s="1">
+        <v>3</v>
+      </c>
+      <c r="H7" s="2">
+        <v>3</v>
+      </c>
+      <c r="I7" s="1">
         <v>15</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="6" t="s">
+      <c r="J7" s="1">
+        <v>70</v>
+      </c>
+      <c r="K7" s="1">
+        <v>5</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="N7" s="1">
         <v>2</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="6" t="s">
+      <c r="O7" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>2007</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="1">
+        <v>3007</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="G8" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="H8" s="2">
+        <v>3</v>
+      </c>
+      <c r="I8" s="1">
+        <v>17</v>
+      </c>
+      <c r="J8" s="1">
+        <v>80</v>
+      </c>
+      <c r="K8" s="1">
         <v>6</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="L8" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="N8" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="O8" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>2008</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="1">
+        <v>3008</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="G9" s="1">
+        <v>3.4</v>
+      </c>
+      <c r="H9" s="2">
+        <v>3</v>
+      </c>
+      <c r="I9" s="1">
+        <v>19</v>
+      </c>
+      <c r="J9" s="1">
+        <v>90</v>
+      </c>
+      <c r="K9" s="1">
         <v>7</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L9" s="1">
+        <v>1.35</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="N9" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="O9" s="1">
+        <v>1.35</v>
+      </c>
+      <c r="P9" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>2009</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3009</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="G10" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="H10" s="2">
+        <v>3</v>
+      </c>
+      <c r="I10" s="1">
+        <v>21</v>
+      </c>
+      <c r="J10" s="1">
+        <v>100</v>
+      </c>
+      <c r="K10" s="1">
         <v>8</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L10" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="N10" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="O10" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="P10" s="1">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>2010</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="1">
+        <v>3010</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="G11" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="H11" s="2">
+        <v>3</v>
+      </c>
+      <c r="I11" s="1">
+        <v>23</v>
+      </c>
+      <c r="J11" s="1">
+        <v>110</v>
+      </c>
+      <c r="K11" s="1">
         <v>9</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>2001</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="12">
-        <v>0</v>
-      </c>
-      <c r="E3" s="8">
-        <v>3001</v>
-      </c>
-      <c r="F3" s="9">
-        <v>1</v>
-      </c>
-      <c r="G3" s="12">
-        <v>0.4</v>
-      </c>
-      <c r="H3" s="8">
-        <v>3</v>
-      </c>
-      <c r="I3" s="8">
-        <v>3</v>
-      </c>
-      <c r="J3" s="9">
-        <v>1.2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>2002</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="12">
-        <v>1</v>
-      </c>
-      <c r="E4" s="8">
-        <v>3002</v>
-      </c>
-      <c r="F4" s="9">
-        <v>1</v>
-      </c>
-      <c r="G4" s="12">
-        <v>0.4</v>
-      </c>
-      <c r="H4" s="8">
-        <v>2.25</v>
-      </c>
-      <c r="I4" s="8">
-        <v>6</v>
-      </c>
-      <c r="J4" s="9">
-        <v>4</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>18</v>
+      <c r="L11" s="1">
+        <v>1.45</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="N11" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="O11" s="1">
+        <v>1.45</v>
+      </c>
+      <c r="P11" s="1">
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:R1"/>
-  </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>

--- a/light_fight/Assets/Excels/MonsterConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterConfig.xlsx
@@ -22,27 +22,27 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="105">
   <si>
-    <t xml:space="preserve">monsterId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monsterName</t>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
   </si>
   <si>
     <t xml:space="preserve">path</t>
   </si>
   <si>
-    <t xml:space="preserve">Threat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
     <t xml:space="preserve">skillId</t>
   </si>
   <si>
     <t xml:space="preserve">skillLevel</t>
   </si>
   <si>
+    <t xml:space="preserve">skillCooldown</t>
+  </si>
+  <si>
     <t xml:space="preserve">radius</t>
   </si>
   <si>
@@ -79,27 +79,27 @@
     <t xml:space="preserve">Baby Alien</t>
   </si>
   <si>
+    <t xml:space="preserve">Chaser</t>
+  </si>
+  <si>
     <t xml:space="preserve">2001 Monster</t>
   </si>
   <si>
-    <t xml:space="preserve">Chaser</t>
+    <t xml:space="preserve">Swarm</t>
   </si>
   <si>
     <t xml:space="preserve">2002 Monster</t>
   </si>
   <si>
-    <t xml:space="preserve">Swarm</t>
-  </si>
-  <si>
     <t xml:space="preserve">Spitter</t>
   </si>
   <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
     <t xml:space="preserve">2003 Monster</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
     <t xml:space="preserve">Charger</t>
   </si>
   <si>
@@ -109,21 +109,21 @@
     <t xml:space="preserve">Pursuer</t>
   </si>
   <si>
+    <t xml:space="preserve">Runner</t>
+  </si>
+  <si>
     <t xml:space="preserve">2005 Monster</t>
   </si>
   <si>
-    <t xml:space="preserve">Runner</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bruiser</t>
   </si>
   <si>
+    <t xml:space="preserve">Tank</t>
+  </si>
+  <si>
     <t xml:space="preserve">2006 Monster</t>
   </si>
   <si>
-    <t xml:space="preserve">Tank</t>
-  </si>
-  <si>
     <t xml:space="preserve">Buffer</t>
   </si>
   <si>
@@ -133,12 +133,12 @@
     <t xml:space="preserve">Fly</t>
   </si>
   <si>
+    <t xml:space="preserve">Flyer</t>
+  </si>
+  <si>
     <t xml:space="preserve">2008 Monster</t>
   </si>
   <si>
-    <t xml:space="preserve">Flyer</t>
-  </si>
-  <si>
     <t xml:space="preserve">Healer</t>
   </si>
   <si>
@@ -148,30 +148,30 @@
     <t xml:space="preserve">Looter</t>
   </si>
   <si>
+    <t xml:space="preserve">Objective</t>
+  </si>
+  <si>
     <t xml:space="preserve">2010 Monster</t>
   </si>
   <si>
-    <t xml:space="preserve">Objective</t>
-  </si>
-  <si>
     <t xml:space="preserve">Helmet Alien</t>
   </si>
   <si>
+    <t xml:space="preserve">Armored</t>
+  </si>
+  <si>
     <t xml:space="preserve">2011 Monster</t>
   </si>
   <si>
-    <t xml:space="preserve">Armored</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fin Alien</t>
   </si>
   <si>
+    <t xml:space="preserve">FastMelee</t>
+  </si>
+  <si>
     <t xml:space="preserve">2012 Monster</t>
   </si>
   <si>
-    <t xml:space="preserve">FastMelee</t>
-  </si>
-  <si>
     <t xml:space="preserve">Spawner</t>
   </si>
   <si>
@@ -205,48 +205,48 @@
     <t xml:space="preserve">Slasher</t>
   </si>
   <si>
+    <t xml:space="preserve">BossMelee</t>
+  </si>
+  <si>
     <t xml:space="preserve">2018 Monster</t>
   </si>
   <si>
-    <t xml:space="preserve">BossMelee</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tentacle</t>
   </si>
   <si>
+    <t xml:space="preserve">Summoner</t>
+  </si>
+  <si>
     <t xml:space="preserve">2019 Monster</t>
   </si>
   <si>
-    <t xml:space="preserve">Summoner</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rhino</t>
   </si>
   <si>
+    <t xml:space="preserve">EliteCharger</t>
+  </si>
+  <si>
     <t xml:space="preserve">2020 Monster</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteCharger</t>
-  </si>
-  <si>
     <t xml:space="preserve">Butcher</t>
   </si>
   <si>
+    <t xml:space="preserve">Elite</t>
+  </si>
+  <si>
     <t xml:space="preserve">2021 Monster</t>
   </si>
   <si>
-    <t xml:space="preserve">Elite</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monk</t>
   </si>
   <si>
+    <t xml:space="preserve">EliteSummoner</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022 Monster</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteSummoner</t>
-  </si>
-  <si>
     <t xml:space="preserve">Croc</t>
   </si>
   <si>
@@ -256,66 +256,66 @@
     <t xml:space="preserve">Colossus</t>
   </si>
   <si>
+    <t xml:space="preserve">TankBoss</t>
+  </si>
+  <si>
     <t xml:space="preserve">2024 Monster</t>
   </si>
   <si>
-    <t xml:space="preserve">TankBoss</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mantis</t>
   </si>
   <si>
+    <t xml:space="preserve">EliteMelee</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025 Monster</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteMelee</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mother</t>
   </si>
   <si>
+    <t xml:space="preserve">SummonBoss</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026 Monster</t>
   </si>
   <si>
-    <t xml:space="preserve">SummonBoss</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gargoyle</t>
   </si>
   <si>
+    <t xml:space="preserve">EliteRanged</t>
+  </si>
+  <si>
     <t xml:space="preserve">2027 Monster</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteRanged</t>
-  </si>
-  <si>
     <t xml:space="preserve">Predator</t>
   </si>
   <si>
+    <t xml:space="preserve">FinalBoss</t>
+  </si>
+  <si>
     <t xml:space="preserve">2028 Monster</t>
   </si>
   <si>
-    <t xml:space="preserve">FinalBoss</t>
-  </si>
-  <si>
     <t xml:space="preserve">Anemone</t>
   </si>
   <si>
+    <t xml:space="preserve">Turret</t>
+  </si>
+  <si>
     <t xml:space="preserve">2029 Monster</t>
   </si>
   <si>
-    <t xml:space="preserve">Turret</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dragonfish</t>
   </si>
   <si>
+    <t xml:space="preserve">HeavyRanged</t>
+  </si>
+  <si>
     <t xml:space="preserve">2030 Monster</t>
   </si>
   <si>
-    <t xml:space="preserve">HeavyRanged</t>
-  </si>
-  <si>
     <t xml:space="preserve">Walrus</t>
   </si>
   <si>
@@ -325,10 +325,10 @@
     <t xml:space="preserve">Goblin Shark</t>
   </si>
   <si>
+    <t xml:space="preserve">Ambusher</t>
+  </si>
+  <si>
     <t xml:space="preserve">2032 Monster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ambusher</t>
   </si>
   <si>
     <t xml:space="preserve">Stonefish</t>
@@ -376,9 +376,16 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
       <right/>
       <top/>
       <bottom/>
@@ -410,16 +417,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -456,13 +471,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="monsters" displayName="monsters" ref="A1:J34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A1:J34"/>
   <tableColumns count="10">
-    <tableColumn id="1" name="monsterId"/>
-    <tableColumn id="2" name="monsterName"/>
-    <tableColumn id="3" name="path"/>
-    <tableColumn id="4" name="Threat"/>
-    <tableColumn id="5" name="description"/>
-    <tableColumn id="6" name="skillId"/>
-    <tableColumn id="7" name="skillLevel"/>
+    <tableColumn id="1" name="id"/>
+    <tableColumn id="2" name="name"/>
+    <tableColumn id="3" name="description"/>
+    <tableColumn id="4" name="path"/>
+    <tableColumn id="5" name="skillId"/>
+    <tableColumn id="6" name="skillLevel"/>
+    <tableColumn id="7" name="skillCooldown"/>
     <tableColumn id="8" name="radius"/>
     <tableColumn id="9" name="moveSpeed"/>
     <tableColumn id="10" name="stopMoveDistance"/>
@@ -650,39 +665,44 @@
   <dimension ref="A1:R34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="1" style="1" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="15.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="11" style="1" width="10.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -720,19 +740,19 @@
       <c r="C2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="E2" s="2" t="n">
+        <v>3001</v>
+      </c>
       <c r="F2" s="1" t="n">
-        <v>3001</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="H2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
@@ -771,24 +791,24 @@
         <v>2002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="E3" s="2" t="n">
+        <v>3002</v>
+      </c>
       <c r="F3" s="1" t="n">
-        <v>3002</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="H3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
@@ -832,19 +852,19 @@
       <c r="C4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="E4" s="2" t="n">
+        <v>3003</v>
+      </c>
       <c r="F4" s="1" t="n">
-        <v>3003</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="H4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
@@ -886,21 +906,21 @@
         <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>26</v>
+      <c r="E5" s="2" t="n">
+        <v>3004</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>3004</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="H5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
@@ -944,19 +964,19 @@
       <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="E6" s="2" t="n">
+        <v>3005</v>
+      </c>
       <c r="F6" s="1" t="n">
-        <v>3005</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="H6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
@@ -1000,19 +1020,19 @@
       <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="E7" s="2" t="n">
+        <v>3006</v>
+      </c>
       <c r="F7" s="1" t="n">
-        <v>3006</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="H7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
@@ -1054,21 +1074,21 @@
         <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>34</v>
+      <c r="E8" s="2" t="n">
+        <v>3007</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>3007</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="H8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
@@ -1112,19 +1132,19 @@
       <c r="C9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="E9" s="2" t="n">
+        <v>3008</v>
+      </c>
       <c r="F9" s="1" t="n">
-        <v>3008</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="H9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I9" s="1" t="n">
@@ -1166,21 +1186,21 @@
         <v>39</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>39</v>
+      <c r="E10" s="2" t="n">
+        <v>3009</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>3009</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="H10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="1" t="n">
@@ -1224,19 +1244,19 @@
       <c r="C11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="E11" s="2" t="n">
+        <v>3010</v>
+      </c>
       <c r="F11" s="1" t="n">
-        <v>3010</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="H11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I11" s="1" t="n">
@@ -1280,19 +1300,19 @@
       <c r="C12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="E12" s="2" t="n">
+        <v>3011</v>
+      </c>
       <c r="F12" s="1" t="n">
-        <v>3011</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="H12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="1" t="n">
@@ -1336,19 +1356,19 @@
       <c r="C13" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="E13" s="2" t="n">
+        <v>3012</v>
+      </c>
       <c r="F13" s="1" t="n">
-        <v>3012</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="H13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I13" s="1" t="n">
@@ -1390,21 +1410,21 @@
         <v>50</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>50</v>
+      <c r="E14" s="2" t="n">
+        <v>3013</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>3013</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="1" t="n">
+      <c r="H14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I14" s="1" t="n">
@@ -1446,21 +1466,21 @@
         <v>52</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>25</v>
+      <c r="E15" s="2" t="n">
+        <v>3014</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>3014</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="1" t="n">
+      <c r="H15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I15" s="1" t="n">
@@ -1502,21 +1522,21 @@
         <v>54</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>33</v>
+      <c r="E16" s="2" t="n">
+        <v>3015</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>3015</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="1" t="n">
+      <c r="H16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="1" t="n">
@@ -1558,21 +1578,21 @@
         <v>56</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>26</v>
+      <c r="E17" s="2" t="n">
+        <v>3016</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>3016</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="1" t="n">
+      <c r="H17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I17" s="1" t="n">
@@ -1614,21 +1634,21 @@
         <v>58</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>43</v>
+      <c r="E18" s="2" t="n">
+        <v>3017</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>3017</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="1" t="n">
+      <c r="H18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I18" s="1" t="n">
@@ -1672,19 +1692,19 @@
       <c r="C19" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="E19" s="2" t="n">
+        <v>3018</v>
+      </c>
       <c r="F19" s="1" t="n">
-        <v>3018</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="1" t="n">
+      <c r="H19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I19" s="1" t="n">
@@ -1728,19 +1748,19 @@
       <c r="C20" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="E20" s="2" t="n">
+        <v>3019</v>
+      </c>
       <c r="F20" s="1" t="n">
-        <v>3019</v>
+        <v>1</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="1" t="n">
+      <c r="H20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I20" s="1" t="n">
@@ -1784,19 +1804,19 @@
       <c r="C21" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>68</v>
       </c>
+      <c r="E21" s="2" t="n">
+        <v>3020</v>
+      </c>
       <c r="F21" s="1" t="n">
-        <v>3020</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="1" t="n">
+      <c r="H21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I21" s="1" t="n">
@@ -1840,19 +1860,19 @@
       <c r="C22" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="E22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="E22" s="2" t="n">
+        <v>3021</v>
+      </c>
       <c r="F22" s="1" t="n">
-        <v>3021</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="1" t="n">
+      <c r="H22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I22" s="1" t="n">
@@ -1896,19 +1916,19 @@
       <c r="C23" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>74</v>
       </c>
+      <c r="E23" s="2" t="n">
+        <v>3022</v>
+      </c>
       <c r="F23" s="1" t="n">
-        <v>3022</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="1" t="n">
+      <c r="H23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I23" s="1" t="n">
@@ -1950,21 +1970,21 @@
         <v>75</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>68</v>
+      <c r="E24" s="2" t="n">
+        <v>3023</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>3023</v>
+        <v>1</v>
       </c>
       <c r="G24" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="1" t="n">
+      <c r="H24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I24" s="1" t="n">
@@ -2008,19 +2028,19 @@
       <c r="C25" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="E25" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>79</v>
       </c>
+      <c r="E25" s="2" t="n">
+        <v>3024</v>
+      </c>
       <c r="F25" s="1" t="n">
-        <v>3024</v>
+        <v>1</v>
       </c>
       <c r="G25" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="1" t="n">
+      <c r="H25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I25" s="1" t="n">
@@ -2064,19 +2084,19 @@
       <c r="C26" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D26" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="E26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>82</v>
       </c>
+      <c r="E26" s="2" t="n">
+        <v>3025</v>
+      </c>
       <c r="F26" s="1" t="n">
-        <v>3025</v>
+        <v>1</v>
       </c>
       <c r="G26" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="1" t="n">
+      <c r="H26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I26" s="1" t="n">
@@ -2120,19 +2140,19 @@
       <c r="C27" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D27" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="E27" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>85</v>
       </c>
+      <c r="E27" s="2" t="n">
+        <v>3026</v>
+      </c>
       <c r="F27" s="1" t="n">
-        <v>3026</v>
+        <v>1</v>
       </c>
       <c r="G27" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="1" t="n">
+      <c r="H27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I27" s="1" t="n">
@@ -2176,19 +2196,19 @@
       <c r="C28" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D28" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="E28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>88</v>
       </c>
+      <c r="E28" s="2" t="n">
+        <v>3027</v>
+      </c>
       <c r="F28" s="1" t="n">
-        <v>3027</v>
+        <v>1</v>
       </c>
       <c r="G28" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="1" t="n">
+      <c r="H28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I28" s="1" t="n">
@@ -2232,19 +2252,19 @@
       <c r="C29" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D29" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>91</v>
       </c>
+      <c r="E29" s="2" t="n">
+        <v>3028</v>
+      </c>
       <c r="F29" s="1" t="n">
-        <v>3028</v>
+        <v>1</v>
       </c>
       <c r="G29" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="1" t="n">
+      <c r="H29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I29" s="1" t="n">
@@ -2288,19 +2308,19 @@
       <c r="C30" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D30" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>94</v>
       </c>
+      <c r="E30" s="2" t="n">
+        <v>3029</v>
+      </c>
       <c r="F30" s="1" t="n">
-        <v>3029</v>
+        <v>1</v>
       </c>
       <c r="G30" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="1" t="n">
+      <c r="H30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I30" s="1" t="n">
@@ -2344,19 +2364,19 @@
       <c r="C31" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D31" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E31" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>97</v>
       </c>
+      <c r="E31" s="2" t="n">
+        <v>3030</v>
+      </c>
       <c r="F31" s="1" t="n">
-        <v>3030</v>
+        <v>1</v>
       </c>
       <c r="G31" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="1" t="n">
+      <c r="H31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I31" s="1" t="n">
@@ -2398,21 +2418,21 @@
         <v>98</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D32" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>26</v>
+      <c r="E32" s="2" t="n">
+        <v>3031</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>3031</v>
+        <v>1</v>
       </c>
       <c r="G32" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="1" t="n">
+      <c r="H32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I32" s="1" t="n">
@@ -2456,19 +2476,19 @@
       <c r="C33" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D33" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E33" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>102</v>
       </c>
+      <c r="E33" s="2" t="n">
+        <v>3032</v>
+      </c>
       <c r="F33" s="1" t="n">
-        <v>3032</v>
+        <v>1</v>
       </c>
       <c r="G33" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="1" t="n">
+      <c r="H33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I33" s="1" t="n">
@@ -2510,21 +2530,21 @@
         <v>103</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D34" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>34</v>
+      <c r="E34" s="2" t="n">
+        <v>3033</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>3033</v>
+        <v>1</v>
       </c>
       <c r="G34" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="1" t="n">
+      <c r="H34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I34" s="1" t="n">

--- a/light_fight/Assets/Excels/MonsterConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="104">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -38,9 +38,6 @@
   </si>
   <si>
     <t xml:space="preserve">skillLevel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skillCooldown</t>
   </si>
   <si>
     <t xml:space="preserve">radius</t>
@@ -417,7 +414,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -428,6 +425,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -468,19 +469,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="monsters" displayName="monsters" ref="A1:J34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:J34"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="monsters" displayName="monsters" ref="A1:I34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I34"/>
+  <tableColumns count="9">
     <tableColumn id="1" name="id"/>
     <tableColumn id="2" name="name"/>
     <tableColumn id="3" name="description"/>
     <tableColumn id="4" name="path"/>
     <tableColumn id="5" name="skillId"/>
     <tableColumn id="6" name="skillLevel"/>
-    <tableColumn id="7" name="skillCooldown"/>
-    <tableColumn id="8" name="radius"/>
-    <tableColumn id="9" name="moveSpeed"/>
-    <tableColumn id="10" name="stopMoveDistance"/>
+    <tableColumn id="7" name="radius"/>
+    <tableColumn id="8" name="moveSpeed"/>
+    <tableColumn id="9" name="stopMoveDistance"/>
   </tableColumns>
 </table>
 </file>
@@ -662,47 +662,48 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="15.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="15.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="15.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="15.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="15.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="11" style="1" width="10.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="10" style="1" width="10.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16383" min="16383" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="3" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -725,9 +726,6 @@
       </c>
       <c r="Q1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -735,13 +733,13 @@
         <v>2001</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>3001</v>
@@ -749,40 +747,37 @@
       <c r="F2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>1</v>
+      <c r="G2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>3.79999995231628</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>3.79999995231628</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>1.20000004768372</v>
+        <v>1</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -791,13 +786,13 @@
         <v>2002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>3002</v>
@@ -805,14 +800,14 @@
       <c r="F3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>1</v>
+      <c r="G3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>4.5</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J3" s="1" t="n">
         <v>1</v>
@@ -821,24 +816,21 @@
         <v>1</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -847,13 +839,13 @@
         <v>2003</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>3003</v>
@@ -861,40 +853,37 @@
       <c r="F4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>1</v>
+      <c r="G4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>3.20000004768372</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>3.20000004768372</v>
+        <v>5</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -903,13 +892,13 @@
         <v>2004</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>3004</v>
@@ -917,40 +906,37 @@
       <c r="F5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>1</v>
+      <c r="G5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>5.5</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="J5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -959,13 +945,13 @@
         <v>2005</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>3005</v>
@@ -973,40 +959,37 @@
       <c r="F6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>1</v>
+      <c r="G6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>6</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>6</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>1.20000004768372</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1015,13 +998,13 @@
         <v>2006</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>3006</v>
@@ -1029,40 +1012,37 @@
       <c r="F7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>1</v>
+      <c r="G7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1071,13 +1051,13 @@
         <v>2007</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>3007</v>
@@ -1085,40 +1065,37 @@
       <c r="F8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>1</v>
+      <c r="G8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>2.5</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1127,13 +1104,13 @@
         <v>2008</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>3008</v>
@@ -1141,40 +1118,37 @@
       <c r="F9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>1</v>
+      <c r="G9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>4.5</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1183,13 +1157,13 @@
         <v>2009</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>3009</v>
@@ -1197,40 +1171,37 @@
       <c r="F10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>1</v>
+      <c r="G10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1239,13 +1210,13 @@
         <v>2010</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>3010</v>
@@ -1253,40 +1224,37 @@
       <c r="F11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>1</v>
+      <c r="G11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>4.5</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1295,13 +1263,13 @@
         <v>2011</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>3011</v>
@@ -1309,40 +1277,37 @@
       <c r="F12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>1</v>
+      <c r="G12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>3.5</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>3.5</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>1.20000004768372</v>
+        <v>1</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1351,13 +1316,13 @@
         <v>2012</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>3012</v>
@@ -1365,40 +1330,37 @@
       <c r="F13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>1</v>
+      <c r="G13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>5.5</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="J13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1407,13 +1369,13 @@
         <v>2013</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>3013</v>
@@ -1421,40 +1383,37 @@
       <c r="F14" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>1</v>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>2.59999990463257</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>2.59999990463257</v>
+        <v>4.5</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1463,13 +1422,13 @@
         <v>2014</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>3014</v>
@@ -1477,40 +1436,37 @@
       <c r="F15" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>1</v>
+      <c r="G15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="I15" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1519,13 +1475,13 @@
         <v>2015</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>3015</v>
@@ -1533,40 +1489,37 @@
       <c r="F16" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>1</v>
+      <c r="G16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="I16" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="L16" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J16" s="1" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="1" t="n">
-        <v>30</v>
-      </c>
       <c r="M16" s="1" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1575,13 +1528,13 @@
         <v>2016</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>3016</v>
@@ -1589,40 +1542,37 @@
       <c r="F17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>1</v>
+      <c r="G17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>5</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>1.20000004768372</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M17" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1631,13 +1581,13 @@
         <v>2017</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>3017</v>
@@ -1645,40 +1595,37 @@
       <c r="F18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>1</v>
+      <c r="G18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="I18" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1687,13 +1634,13 @@
         <v>2018</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>3018</v>
@@ -1701,40 +1648,37 @@
       <c r="F19" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>1</v>
+      <c r="G19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>3.5</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="K19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="M19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" s="1" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O19" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="P19" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1743,13 +1687,13 @@
         <v>2019</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>3019</v>
@@ -1757,40 +1701,37 @@
       <c r="F20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>1</v>
+      <c r="G20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>2.40000009536743</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>2.40000009536743</v>
+        <v>4</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P20" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1799,13 +1740,13 @@
         <v>2020</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>3020</v>
@@ -1813,40 +1754,37 @@
       <c r="F21" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>1</v>
+      <c r="G21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>6.5</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>3</v>
+        <v>500</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>500</v>
+        <v>5</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>0.8</v>
+        <v>0.05</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>0.05</v>
+        <v>1.8</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" s="1" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -1855,13 +1793,13 @@
         <v>2021</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>3021</v>
@@ -1869,40 +1807,37 @@
       <c r="F22" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>1</v>
+      <c r="G22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>3.79999995231628</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>3.79999995231628</v>
+        <v>2</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>3</v>
+        <v>500</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>500</v>
+        <v>4</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>0.6</v>
+        <v>0.05</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>0.05</v>
+        <v>1.8</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" s="1" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -1911,13 +1846,13 @@
         <v>2022</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>3022</v>
@@ -1925,40 +1860,37 @@
       <c r="F23" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>1</v>
+      <c r="G23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J23" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="L23" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="K23" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="L23" s="1" t="n">
-        <v>400</v>
-      </c>
       <c r="M23" s="1" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>0.7</v>
+        <v>0.05</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>0.05</v>
+        <v>1.8</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" s="1" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -1967,13 +1899,13 @@
         <v>2023</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>3023</v>
@@ -1981,40 +1913,37 @@
       <c r="F24" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>1</v>
+      <c r="G24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>6</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>6</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>1.20000004768372</v>
+        <v>3</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>3</v>
+        <v>500</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>500</v>
+        <v>5</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>0.05</v>
+        <v>1.8</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" s="1" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -2023,13 +1952,13 @@
         <v>2024</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>3024</v>
@@ -2037,40 +1966,37 @@
       <c r="F25" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>1</v>
+      <c r="G25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>1.79999995231628</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>1.79999995231628</v>
+        <v>2.5</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>3</v>
+        <v>550</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>550</v>
+        <v>6</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>0.05</v>
+        <v>1.8</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" s="1" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -2079,13 +2005,13 @@
         <v>2025</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>3025</v>
@@ -2093,40 +2019,37 @@
       <c r="F26" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>1</v>
+      <c r="G26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="I26" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J26" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" s="1" t="n">
+        <v>450</v>
+      </c>
+      <c r="L26" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J26" s="1" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K26" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="L26" s="1" t="n">
-        <v>450</v>
-      </c>
       <c r="M26" s="1" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>0.7</v>
+        <v>0.05</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>0.05</v>
+        <v>1.8</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" s="1" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -2135,13 +2058,13 @@
         <v>2026</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>3026</v>
@@ -2149,40 +2072,37 @@
       <c r="F27" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>1</v>
+      <c r="G27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>2.20000004768372</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>2.20000004768372</v>
+        <v>4</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>500</v>
+        <v>3</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>1.2</v>
+        <v>0.05</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>0.05</v>
+        <v>1.8</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" s="1" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -2191,13 +2111,13 @@
         <v>2027</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>3027</v>
@@ -2205,40 +2125,37 @@
       <c r="F28" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>1</v>
+      <c r="G28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="I28" s="1" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J28" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="L28" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="1" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K28" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" s="1" t="n">
-        <v>400</v>
-      </c>
       <c r="M28" s="1" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>0.6</v>
+        <v>0.05</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>0.05</v>
+        <v>1.8</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R28" s="1" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -2247,13 +2164,13 @@
         <v>2028</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>3028</v>
@@ -2261,40 +2178,37 @@
       <c r="F29" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>1</v>
+      <c r="G29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>4.5</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2303,13 +2217,13 @@
         <v>2029</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>3029</v>
@@ -2317,40 +2231,37 @@
       <c r="F30" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>1</v>
+      <c r="G30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2359,13 +2270,13 @@
         <v>2030</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>3030</v>
@@ -2373,40 +2284,37 @@
       <c r="F31" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>1</v>
+      <c r="G31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>3.5</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2415,13 +2323,13 @@
         <v>2031</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>3031</v>
@@ -2429,40 +2337,37 @@
       <c r="F32" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G32" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>1</v>
+      <c r="G32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K32" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="L32" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L32" s="1" t="n">
-        <v>40</v>
-      </c>
       <c r="M32" s="1" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2471,13 +2376,13 @@
         <v>2032</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>3032</v>
@@ -2485,40 +2390,37 @@
       <c r="F33" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>1</v>
+      <c r="G33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2527,13 +2429,13 @@
         <v>2033</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>3033</v>
@@ -2541,40 +2443,37 @@
       <c r="F34" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G34" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>1</v>
+      <c r="G34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" s="1" t="n">
         <v>0</v>
       </c>
     </row>

--- a/light_fight/Assets/Excels/MonsterConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="54">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -58,7 +58,7 @@
     <t xml:space="preserve">ColliderOffset</t>
   </si>
   <si>
-    <t xml:space="preserve">HpBarOffset</t>
+    <t xml:space="preserve">HealthBarOffset</t>
   </si>
   <si>
     <t xml:space="preserve">FloatingTextOffset</t>
@@ -80,6 +80,9 @@
   </si>
   <si>
     <t xml:space="preserve">1,3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">null</t>
   </si>
   <si>
     <t xml:space="preserve">0,0</t>
@@ -269,7 +272,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -282,11 +285,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -558,7 +557,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="2" style="1" width="19.46"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="1" max="9" min="8" style="1" width="19.46"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="10" style="1" width="19.46"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="10" style="1" width="19.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="20.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="23.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="27.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="30.51"/>
@@ -571,55 +571,55 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -633,13 +633,13 @@
       <c r="C2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G2" s="1" t="n">
@@ -648,6 +648,9 @@
       <c r="H2" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J2" s="1" t="n">
         <v>1</v>
       </c>
@@ -655,13 +658,13 @@
         <v>1</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O2" s="1" t="n">
         <v>0</v>
@@ -681,26 +684,29 @@
         <v>90002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="5" t="n">
+      <c r="F3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I3" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J3" s="1" t="n">
         <v>1</v>
       </c>
@@ -708,13 +714,13 @@
         <v>1</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O3" s="1" t="n">
         <v>0</v>
@@ -734,18 +740,18 @@
         <v>90003</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="D4" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="1" t="n">
@@ -754,6 +760,9 @@
       <c r="H4" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I4" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J4" s="1" t="n">
         <v>1</v>
       </c>
@@ -761,13 +770,13 @@
         <v>1</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>0</v>
@@ -787,26 +796,29 @@
         <v>90004</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="5" t="n">
+      <c r="F5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I5" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J5" s="1" t="n">
         <v>1</v>
       </c>
@@ -814,13 +826,13 @@
         <v>1</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O5" s="1" t="n">
         <v>0</v>
@@ -840,18 +852,18 @@
         <v>90005</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="1" t="n">
@@ -860,6 +872,9 @@
       <c r="H6" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I6" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J6" s="1" t="n">
         <v>1</v>
       </c>
@@ -867,13 +882,13 @@
         <v>1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O6" s="1" t="n">
         <v>0</v>
@@ -893,26 +908,29 @@
         <v>90006</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>6</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="5" t="n">
+      <c r="F7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I7" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J7" s="1" t="n">
         <v>1</v>
       </c>
@@ -920,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O7" s="1" t="n">
         <v>0</v>
@@ -946,18 +964,18 @@
         <v>90007</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="D8" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G8" s="1" t="n">
@@ -966,6 +984,9 @@
       <c r="H8" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I8" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J8" s="1" t="n">
         <v>1</v>
       </c>
@@ -973,13 +994,13 @@
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O8" s="1" t="n">
         <v>0</v>
@@ -999,26 +1020,29 @@
         <v>90008</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>8</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="5" t="n">
+      <c r="F9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I9" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J9" s="1" t="n">
         <v>1</v>
       </c>
@@ -1026,13 +1050,13 @@
         <v>1</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O9" s="1" t="n">
         <v>0</v>
@@ -1052,18 +1076,18 @@
         <v>90009</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>9</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G10" s="1" t="n">
@@ -1072,7 +1096,9 @@
       <c r="H10" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="5"/>
+      <c r="I10" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J10" s="1" t="n">
         <v>1</v>
       </c>
@@ -1080,13 +1106,13 @@
         <v>1</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O10" s="1" t="n">
         <v>0</v>
@@ -1106,27 +1132,29 @@
         <v>90010</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D11" s="4" t="n">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="5" t="n">
+      <c r="F11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="5"/>
+      <c r="I11" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J11" s="1" t="n">
         <v>1</v>
       </c>
@@ -1134,13 +1162,13 @@
         <v>1</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O11" s="1" t="n">
         <v>0</v>
@@ -1160,18 +1188,18 @@
         <v>90011</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="D12" s="4" t="n">
         <v>11</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G12" s="1" t="n">
@@ -1180,7 +1208,9 @@
       <c r="H12" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="5"/>
+      <c r="I12" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J12" s="1" t="n">
         <v>1</v>
       </c>
@@ -1188,13 +1218,13 @@
         <v>1</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O12" s="1" t="n">
         <v>0</v>
@@ -1214,27 +1244,29 @@
         <v>90012</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D13" s="4" t="n">
         <v>12</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="5" t="n">
+      <c r="F13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="5"/>
+      <c r="I13" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J13" s="1" t="n">
         <v>1</v>
       </c>
@@ -1242,13 +1274,13 @@
         <v>1</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O13" s="1" t="n">
         <v>0</v>
@@ -1268,18 +1300,18 @@
         <v>90013</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="D14" s="4" t="n">
         <v>13</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>4.5</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G14" s="1" t="n">
@@ -1288,7 +1320,9 @@
       <c r="H14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="5"/>
+      <c r="I14" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J14" s="1" t="n">
         <v>1</v>
       </c>
@@ -1296,13 +1330,13 @@
         <v>1</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O14" s="1" t="n">
         <v>0</v>
@@ -1322,27 +1356,29 @@
         <v>90014</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="D15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="5" t="n">
+      <c r="F15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="5"/>
+      <c r="I15" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J15" s="1" t="n">
         <v>1</v>
       </c>
@@ -1350,13 +1386,13 @@
         <v>1</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O15" s="1" t="n">
         <v>0</v>
@@ -1376,18 +1412,18 @@
         <v>90015</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="D16" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G16" s="1" t="n">
@@ -1396,7 +1432,9 @@
       <c r="H16" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="5"/>
+      <c r="I16" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J16" s="1" t="n">
         <v>1</v>
       </c>
@@ -1404,13 +1442,13 @@
         <v>1</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O16" s="1" t="n">
         <v>0</v>
@@ -1430,27 +1468,29 @@
         <v>90016</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="D17" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" s="5" t="n">
+      <c r="F17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="5"/>
+      <c r="I17" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J17" s="1" t="n">
         <v>1</v>
       </c>
@@ -1458,13 +1498,13 @@
         <v>1</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O17" s="1" t="n">
         <v>0</v>
@@ -1484,18 +1524,18 @@
         <v>90017</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="D18" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G18" s="1" t="n">
@@ -1504,7 +1544,9 @@
       <c r="H18" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="5"/>
+      <c r="I18" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J18" s="1" t="n">
         <v>1</v>
       </c>
@@ -1512,13 +1554,13 @@
         <v>1</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O18" s="1" t="n">
         <v>0</v>
@@ -1538,27 +1580,29 @@
         <v>90018</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="D19" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" s="5" t="n">
+      <c r="F19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="5"/>
+      <c r="I19" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J19" s="1" t="n">
         <v>1</v>
       </c>
@@ -1566,13 +1610,13 @@
         <v>1</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O19" s="1" t="n">
         <v>0</v>
@@ -1592,18 +1636,18 @@
         <v>90019</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="D20" s="4" t="n">
         <v>6</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G20" s="1" t="n">
@@ -1612,7 +1656,9 @@
       <c r="H20" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="5"/>
+      <c r="I20" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J20" s="1" t="n">
         <v>1</v>
       </c>
@@ -1620,13 +1666,13 @@
         <v>1</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O20" s="1" t="n">
         <v>0</v>
@@ -1646,27 +1692,29 @@
         <v>90020</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="D21" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="5" t="n">
+      <c r="F21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="5"/>
+      <c r="I21" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J21" s="1" t="n">
         <v>1</v>
       </c>
@@ -1674,13 +1722,13 @@
         <v>1</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O21" s="1" t="n">
         <v>0</v>
@@ -1700,18 +1748,18 @@
         <v>90021</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="D22" s="4" t="n">
         <v>8</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="1" t="n">
@@ -1720,7 +1768,9 @@
       <c r="H22" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="5"/>
+      <c r="I22" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J22" s="1" t="n">
         <v>1</v>
       </c>
@@ -1728,13 +1778,13 @@
         <v>1</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O22" s="1" t="n">
         <v>0</v>
@@ -1754,27 +1804,29 @@
         <v>90022</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="D23" s="4" t="n">
         <v>9</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" s="5" t="n">
+      <c r="F23" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="5"/>
+      <c r="I23" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J23" s="1" t="n">
         <v>1</v>
       </c>
@@ -1782,13 +1834,13 @@
         <v>1</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O23" s="1" t="n">
         <v>0</v>
@@ -1808,18 +1860,18 @@
         <v>90023</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="D24" s="4" t="n">
         <v>10</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="n">
@@ -1828,6 +1880,9 @@
       <c r="H24" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I24" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J24" s="1" t="n">
         <v>1</v>
       </c>
@@ -1835,13 +1890,13 @@
         <v>1</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O24" s="1" t="n">
         <v>0</v>
@@ -1861,26 +1916,29 @@
         <v>90024</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="D25" s="4" t="n">
         <v>11</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>2.5</v>
       </c>
-      <c r="F25" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G25" s="5" t="n">
+      <c r="F25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I25" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J25" s="1" t="n">
         <v>1</v>
       </c>
@@ -1888,13 +1946,13 @@
         <v>1</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O25" s="1" t="n">
         <v>0</v>
@@ -1914,18 +1972,18 @@
         <v>90025</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="D26" s="4" t="n">
         <v>12</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G26" s="1" t="n">
@@ -1934,6 +1992,9 @@
       <c r="H26" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I26" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J26" s="1" t="n">
         <v>1</v>
       </c>
@@ -1941,13 +2002,13 @@
         <v>1</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O26" s="1" t="n">
         <v>0</v>
@@ -1967,26 +2028,29 @@
         <v>90026</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="D27" s="4" t="n">
         <v>13</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F27" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" s="5" t="n">
+      <c r="F27" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I27" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J27" s="1" t="n">
         <v>1</v>
       </c>
@@ -1994,13 +2058,13 @@
         <v>1</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O27" s="1" t="n">
         <v>0</v>
@@ -2020,18 +2084,18 @@
         <v>90027</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D28" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="D28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>6.5</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G28" s="1" t="n">
@@ -2040,6 +2104,9 @@
       <c r="H28" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I28" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J28" s="1" t="n">
         <v>1</v>
       </c>
@@ -2047,13 +2114,13 @@
         <v>1</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O28" s="1" t="n">
         <v>0</v>
@@ -2073,26 +2140,29 @@
         <v>90028</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D29" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="D29" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="F29" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G29" s="5" t="n">
+      <c r="F29" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I29" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J29" s="1" t="n">
         <v>1</v>
       </c>
@@ -2100,13 +2170,13 @@
         <v>1</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O29" s="1" t="n">
         <v>0</v>
@@ -2126,18 +2196,18 @@
         <v>90029</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D30" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="D30" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E30" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="F30" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G30" s="1" t="n">
@@ -2146,6 +2216,9 @@
       <c r="H30" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I30" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J30" s="1" t="n">
         <v>1</v>
       </c>
@@ -2153,13 +2226,13 @@
         <v>1</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O30" s="1" t="n">
         <v>0</v>
@@ -2179,26 +2252,29 @@
         <v>90030</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D31" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D31" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E31" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G31" s="5" t="n">
+      <c r="F31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I31" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J31" s="1" t="n">
         <v>1</v>
       </c>
@@ -2206,13 +2282,13 @@
         <v>1</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O31" s="1" t="n">
         <v>0</v>
@@ -2232,18 +2308,18 @@
         <v>90031</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D32" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="D32" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E32" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G32" s="1" t="n">
@@ -2252,6 +2328,9 @@
       <c r="H32" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I32" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J32" s="1" t="n">
         <v>1</v>
       </c>
@@ -2259,13 +2338,13 @@
         <v>1</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O32" s="1" t="n">
         <v>0</v>
@@ -2285,26 +2364,29 @@
         <v>90032</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D33" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="D33" s="4" t="n">
         <v>6</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="F33" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G33" s="5" t="n">
+      <c r="F33" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I33" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J33" s="1" t="n">
         <v>1</v>
       </c>
@@ -2312,13 +2394,13 @@
         <v>1</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O33" s="1" t="n">
         <v>0</v>
@@ -2338,18 +2420,18 @@
         <v>90033</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="D34" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G34" s="1" t="n">
@@ -2358,6 +2440,9 @@
       <c r="H34" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I34" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J34" s="1" t="n">
         <v>1</v>
       </c>
@@ -2365,13 +2450,13 @@
         <v>1</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O34" s="1" t="n">
         <v>0</v>
@@ -2387,28 +2472,28 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C51:G419 F35:G50">

--- a/light_fight/Assets/Excels/MonsterConfig.xlsx
+++ b/light_fight/Assets/Excels/MonsterConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="52">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -80,12 +80,6 @@
   </si>
   <si>
     <t xml:space="preserve">1,3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0,0</t>
   </si>
   <si>
     <t xml:space="preserve">Chaser</t>
@@ -642,41 +636,11 @@
       <c r="F2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K2" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -684,10 +648,10 @@
         <v>90002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>2</v>
@@ -698,41 +662,12 @@
       <c r="F3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="G3" s="4"/>
       <c r="J3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -740,10 +675,10 @@
         <v>90003</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>3</v>
@@ -754,41 +689,11 @@
       <c r="F4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -796,10 +701,10 @@
         <v>90004</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>4</v>
@@ -810,41 +715,12 @@
       <c r="F5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="G5" s="4"/>
       <c r="J5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -852,10 +728,10 @@
         <v>90005</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>5</v>
@@ -866,41 +742,11 @@
       <c r="F6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -908,10 +754,10 @@
         <v>90006</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>6</v>
@@ -922,41 +768,12 @@
       <c r="F7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="G7" s="4"/>
       <c r="J7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -964,10 +781,10 @@
         <v>90007</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>7</v>
@@ -978,41 +795,11 @@
       <c r="F8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1020,10 +807,10 @@
         <v>90008</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>8</v>
@@ -1034,41 +821,12 @@
       <c r="F9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="G9" s="4"/>
       <c r="J9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1076,10 +834,10 @@
         <v>90009</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>9</v>
@@ -1090,41 +848,11 @@
       <c r="F10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1132,10 +860,10 @@
         <v>90010</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>10</v>
@@ -1146,41 +874,12 @@
       <c r="F11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="G11" s="4"/>
       <c r="J11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1188,10 +887,10 @@
         <v>90011</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>11</v>
@@ -1202,41 +901,11 @@
       <c r="F12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1244,10 +913,10 @@
         <v>90012</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>12</v>
@@ -1258,41 +927,12 @@
       <c r="F13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="G13" s="4"/>
       <c r="J13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1300,10 +940,10 @@
         <v>90013</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>13</v>
@@ -1314,41 +954,11 @@
       <c r="F14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1356,10 +966,10 @@
         <v>90014</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>1</v>
@@ -1370,41 +980,12 @@
       <c r="F15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="G15" s="4"/>
       <c r="J15" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1412,10 +993,10 @@
         <v>90015</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>2</v>
@@ -1426,41 +1007,11 @@
       <c r="F16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1468,10 +1019,10 @@
         <v>90016</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>3</v>
@@ -1482,41 +1033,12 @@
       <c r="F17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="G17" s="4"/>
       <c r="J17" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1524,10 +1046,10 @@
         <v>90017</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>4</v>
@@ -1538,41 +1060,11 @@
       <c r="F18" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1580,10 +1072,10 @@
         <v>90018</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>5</v>
@@ -1594,41 +1086,12 @@
       <c r="F19" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="G19" s="4"/>
       <c r="J19" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1636,10 +1099,10 @@
         <v>90019</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>6</v>
@@ -1650,41 +1113,11 @@
       <c r="F20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1692,10 +1125,10 @@
         <v>90020</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>7</v>
@@ -1706,41 +1139,12 @@
       <c r="F21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="G21" s="4"/>
       <c r="J21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1748,10 +1152,10 @@
         <v>90021</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>8</v>
@@ -1762,41 +1166,11 @@
       <c r="F22" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K22" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1804,10 +1178,10 @@
         <v>90022</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>9</v>
@@ -1818,41 +1192,12 @@
       <c r="F23" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="G23" s="4"/>
       <c r="J23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1860,10 +1205,10 @@
         <v>90023</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>10</v>
@@ -1874,41 +1219,11 @@
       <c r="F24" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J24" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1916,10 +1231,10 @@
         <v>90024</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>11</v>
@@ -1930,41 +1245,12 @@
       <c r="F25" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="G25" s="4"/>
       <c r="J25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1972,10 +1258,10 @@
         <v>90025</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D26" s="4" t="n">
         <v>12</v>
@@ -1986,41 +1272,11 @@
       <c r="F26" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G26" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J26" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K26" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2028,10 +1284,10 @@
         <v>90026</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>13</v>
@@ -2042,41 +1298,12 @@
       <c r="F27" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="G27" s="4"/>
       <c r="J27" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K27" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2084,10 +1311,10 @@
         <v>90027</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>1</v>
@@ -2098,41 +1325,11 @@
       <c r="F28" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K28" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O28" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2140,10 +1337,10 @@
         <v>90028</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D29" s="4" t="n">
         <v>2</v>
@@ -2154,41 +1351,12 @@
       <c r="F29" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="G29" s="4"/>
       <c r="J29" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K29" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M29" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2196,10 +1364,10 @@
         <v>90029</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>3</v>
@@ -2210,41 +1378,11 @@
       <c r="F30" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J30" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2252,10 +1390,10 @@
         <v>90030</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>4</v>
@@ -2266,41 +1404,12 @@
       <c r="F31" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="G31" s="4"/>
       <c r="J31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K31" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O31" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2308,10 +1417,10 @@
         <v>90031</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>5</v>
@@ -2322,41 +1431,11 @@
       <c r="F32" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J32" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2364,10 +1443,10 @@
         <v>90032</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>6</v>
@@ -2378,41 +1457,12 @@
       <c r="F33" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="G33" s="4"/>
       <c r="J33" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K33" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O33" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2420,10 +1470,10 @@
         <v>90033</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>7</v>
@@ -2434,41 +1484,11 @@
       <c r="F34" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G34" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K34" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M34" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O34" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
